--- a/business-libraries/test-data/self_growth/attribution.xlsx
+++ b/business-libraries/test-data/self_growth/attribution.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="⑤b 归因-计算变量" sheetId="1" r:id="rId1"/>
-    <sheet name="⑤c 归因-分级规则" sheetId="2" r:id="rId2"/>
-    <sheet name="⑥ 归因-红线熔断" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤c 归因项" sheetId="2" r:id="rId2"/>
+    <sheet name="⑤d 证据规则" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤e 分级规则" sheetId="4" r:id="rId4"/>
+    <sheet name="⑥ 归因-红线熔断" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,7 +428,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>总负荷指数</v>
+        <v>状态总分</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
@@ -435,379 +437,928 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>五题得分总和</v>
+        <v>状态五问总分，反向题已折算</v>
       </c>
       <c r="E2" t="str">
         <v>SG_FIVE_Q</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>q1-q5</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>情绪耗竭指数</v>
-      </c>
-      <c r="B3" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C3" t="str">
-        <v>维度[EMOTION]</v>
-      </c>
-      <c r="D3" t="str">
-        <v>情绪状态维度均值</v>
-      </c>
-      <c r="E3" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
-      <c r="F3" t="str">
-        <v>q1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>EMOTION</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>连续低意义感次数</v>
-      </c>
-      <c r="B4" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C4" t="str">
-        <v>COUNT_CONSECUTIVE(题[q3] &lt;= 2, 4)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>统计最近连续4次评估中意义感知得分&lt;=2的次数</v>
-      </c>
-      <c r="E4" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
-      <c r="F4" t="str">
-        <v>q3</v>
-      </c>
-      <c r="G4" t="str">
-        <v>MEANING</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>规则编码*</v>
+        <v>归因编码*</v>
       </c>
       <c r="B1" t="str">
+        <v>归因名称*</v>
+      </c>
+      <c r="C1" t="str">
         <v>所属模块*</v>
       </c>
-      <c r="C1" t="str">
-        <v>依据量表编码*</v>
-      </c>
       <c r="D1" t="str">
-        <v>优先级*</v>
+        <v>权重基数*</v>
       </c>
       <c r="E1" t="str">
-        <v>触发条件</v>
+        <v>工具标签*</v>
       </c>
       <c r="F1" t="str">
-        <v>命中等级*</v>
+        <v>归因说明</v>
       </c>
       <c r="G1" t="str">
-        <v>等级中文名*</v>
+        <v>高分表现</v>
       </c>
       <c r="H1" t="str">
-        <v>是否红线熔断*</v>
+        <v>典型诱因</v>
       </c>
       <c r="I1" t="str">
-        <v>主归因*</v>
+        <v>建议动作</v>
       </c>
       <c r="J1" t="str">
-        <v>次归因</v>
-      </c>
-      <c r="K1" t="str">
-        <v>归因理由*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>工具标签*</v>
-      </c>
-      <c r="M1" t="str">
-        <v>结果说明*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>输出动作摘要</v>
-      </c>
-      <c r="O1" t="str">
-        <v>输出工具摘要</v>
-      </c>
-      <c r="P1" t="str">
-        <v>升级条件</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>升级目标</v>
-      </c>
-      <c r="R1" t="str">
-        <v>复评触发条件</v>
-      </c>
-      <c r="S1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG-RED-Q1-Q3</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="B2" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="C2" t="str">
         <v>self_growth</v>
       </c>
-      <c r="C2" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
       <c r="D2" t="str">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>self_growth,emotion,pressure</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>教师的情绪资源被持续消耗且难以自然恢复，是职业倦怠的核心成分。</v>
       </c>
       <c r="G2" t="str">
-        <v>需立即关注</v>
+        <v>晨起即感疲惫、对学生反应变钝、下班后无力社交</v>
       </c>
       <c r="H2" t="str">
-        <v>是</v>
+        <v>长期高强度班务叠加缺乏恢复时段</v>
       </c>
       <c r="I2" t="str">
-        <v>疲惫与意义感同时告急</v>
+        <v>本周内安排两段各 30 分钟的不可打扰恢复时段，并减少一项非必要班务承接</v>
       </c>
       <c r="J2" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Q1疲劳&gt;=4分且Q3意义感&lt;=2分，两者同时处于高危水平，教师可能正经历情绪耗竭的核心阶段</v>
-      </c>
-      <c r="L2" t="str">
-        <v>self_growth,orange,pressure</v>
-      </c>
-      <c r="M2" t="str">
-        <v>疲惫与意义感同时告急风险同时处于高位，已暂停常规建议并转介。</v>
-      </c>
-      <c r="N2" t="str">
-        <v>建议安排心理专员面谈，暂缓常规班级评估</v>
-      </c>
-      <c r="O2" t="str">
-        <v>三分钟补能法（应急）、情绪温度计自评</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>下次评估Q1或Q3任一&gt;=3分时触发复评</v>
-      </c>
-      <c r="S2" t="str">
-        <v>PRD 8.2.1</v>
+        <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG-ORANGE</v>
+        <v>SG_AT_BOUNDARY</v>
       </c>
       <c r="B3" t="str">
+        <v>角色边界失守</v>
+      </c>
+      <c r="C3" t="str">
         <v>self_growth</v>
       </c>
-      <c r="C3" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
       <c r="D3" t="str">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 17</v>
+        <v>self_growth,boundary</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>教师把超出职责范围的责任持续揽在自己身上，导致负荷不可控。</v>
       </c>
       <c r="G3" t="str">
-        <v>需关注</v>
+        <v>认为「什么都是我的责任」、难以拒绝额外要求、下班后仍在处理班务</v>
       </c>
       <c r="H3" t="str">
-        <v>否</v>
+        <v>学校分工不清或教师自我期待过高</v>
       </c>
       <c r="I3" t="str">
-        <v>整体状态偏高</v>
+        <v>做一次职责边界盘点，把当前压力拆成可控制、可影响、暂时不可控三类，只推进可控的一项</v>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>总分&gt;=17分，教师在多个维度上感受到压力，但未达到红线阈值</v>
-      </c>
-      <c r="L3" t="str">
-        <v>self_growth,orange,selfcare</v>
-      </c>
-      <c r="M3" t="str">
-        <v>您的整体状态在多个维度上偏高，建议重点关注并选择1-2项工具开始调整。</v>
-      </c>
-      <c r="N3" t="str">
-        <v>建议本月内完成一次深度自评</v>
-      </c>
-      <c r="O3" t="str">
-        <v>能量记录卡、同伴支持圈</v>
-      </c>
-      <c r="P3" t="str">
-        <v>连续3次评估仍为orange</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>升级至red评估流程</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v>PRD 8.2.1</v>
+        <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG-YELLOW</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="B4" t="str">
+        <v>意义感流失</v>
+      </c>
+      <c r="C4" t="str">
         <v>self_growth</v>
       </c>
-      <c r="C4" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="str">
-        <v>维度[EMOTION] &gt;= 3.5</v>
+        <v>self_growth,meaning</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>教师对班主任工作的价值感知下降，是需要重点关注的信号。</v>
       </c>
       <c r="G4" t="str">
-        <v>需留意</v>
+        <v>反复怀疑工作的价值、对学生的进步不再有反应</v>
       </c>
       <c r="H4" t="str">
-        <v>否</v>
+        <v>长期付出未获反馈，或经历重大挫败事件</v>
       </c>
       <c r="I4" t="str">
-        <v>情绪耗竭需关注</v>
+        <v>记录一件本周确实因为你而变好的小事，并找一位同伴讲给他听</v>
       </c>
       <c r="J4" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K4" t="str">
-        <v>情绪耗竭维度得分偏高，可能出现轻度职业倦怠的早期信号</v>
-      </c>
-      <c r="L4" t="str">
-        <v>self_growth,yellow,peer</v>
-      </c>
-      <c r="M4" t="str">
-        <v>您的情绪耗竭维度偏高，建议开始关注自我照顾。</v>
-      </c>
-      <c r="N4" t="str">
-        <v>建议使用自我照顾工具</v>
-      </c>
-      <c r="O4" t="str">
-        <v>能量记录卡、同伴支持圈</v>
-      </c>
-      <c r="P4" t="str">
-        <v>连续2次评估仍为yellow</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>升级至orange评估流程</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v>PRD 8.2.1</v>
+        <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG-GREEN</v>
+        <v>SG_AT_EFFICACY</v>
       </c>
       <c r="B5" t="str">
+        <v>效能感不足</v>
+      </c>
+      <c r="C5" t="str">
         <v>self_growth</v>
       </c>
-      <c r="C5" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
       <c r="D5" t="str">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>self_growth,efficacy</v>
       </c>
       <c r="F5" t="str">
-        <v>green</v>
+        <v>教师对自己处理复杂问题的能力缺乏信心，容易回避而非应对。</v>
       </c>
       <c r="G5" t="str">
-        <v>状态良好</v>
+        <v>遇到难题先想到「我搞不定」、倾向于上交问题</v>
       </c>
       <c r="H5" t="str">
-        <v>否</v>
+        <v>缺少可复用的方法储备或成功经验</v>
       </c>
       <c r="I5" t="str">
-        <v>状态稳定</v>
+        <v>选一个最小的难题，用一个具体工具完整走一遍并记录结果</v>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>当前评估未触发任何风险规则，教师整体状态稳定</v>
-      </c>
-      <c r="L5" t="str">
-        <v>self_growth,green</v>
-      </c>
-      <c r="M5" t="str">
-        <v>当前状态整体稳定，保持现有节奏即可。</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v>PRD 8.2.1</v>
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SG_AT_SUPPORT</v>
+      </c>
+      <c r="B6" t="str">
+        <v>支持系统缺失</v>
+      </c>
+      <c r="C6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>self_growth,support</v>
+      </c>
+      <c r="F6" t="str">
+        <v>教师遇到困难时缺少可求助的同伴或制度通道，独自消化问题。</v>
+      </c>
+      <c r="G6" t="str">
+        <v>独自消化问题、不主动求助、认为求助等于无能</v>
+      </c>
+      <c r="H6" t="str">
+        <v>教研组协作弱或校内缺少同伴支持机制</v>
+      </c>
+      <c r="I6" t="str">
+        <v>本周找一位同事做一次 20 分钟的结构化复盘，只说事实、感受和需要的支持</v>
+      </c>
+      <c r="J6" t="str">
+        <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>证据编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>触发条件*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>证据权重*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>证据说明*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SG_EV_01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SG_AT_EXHAUST</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D2" t="str">
+        <v>题[q1] &gt;= 4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="str">
+        <v>疲惫题项处于高位，情绪资源已被大量消耗</v>
+      </c>
+      <c r="G2" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SG_EV_02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SG_AT_EXHAUST</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D3" t="str">
+        <v>题[q1] &gt;= 3</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>疲惫题项高于常模均值，处于早期消耗阶段</v>
+      </c>
+      <c r="G3" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SG_EV_03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SG_AT_BOUNDARY</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D4" t="str">
+        <v>题[q2] &gt;= 4</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F4" t="str">
+        <v>频繁出现「什么都是我的责任」的感受</v>
+      </c>
+      <c r="G4" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SG_EV_04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SG_AT_BOUNDARY</v>
+      </c>
+      <c r="C5" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D5" t="str">
+        <v>题[q2] &gt;= 3</v>
+      </c>
+      <c r="E5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>责任边界开始模糊</v>
+      </c>
+      <c r="G5" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SG_EV_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SG_AT_MEANING</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D6" t="str">
+        <v>题[q3] &gt;= 4</v>
+      </c>
+      <c r="E6" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" t="str">
+        <v>意义感知处于低位（反向计分后得分高）</v>
+      </c>
+      <c r="G6" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SG_EV_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>SG_AT_MEANING</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D7" t="str">
+        <v>题[q3] &gt;= 3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>意义感出现波动</v>
+      </c>
+      <c r="G7" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG_EV_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>SG_AT_EFFICACY</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D8" t="str">
+        <v>题[q4] &gt;= 4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>面对复杂问题时效能信心不足</v>
+      </c>
+      <c r="G8" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG_EV_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SG_AT_EFFICACY</v>
+      </c>
+      <c r="C9" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D9" t="str">
+        <v>题[q4] &gt;= 3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>效能信心有所下降</v>
+      </c>
+      <c r="G9" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG_EV_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>SG_AT_SUPPORT</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D10" t="str">
+        <v>题[q5] &gt;= 4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>工作困难长期无人分担</v>
+      </c>
+      <c r="G10" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG_EV_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SG_AT_SUPPORT</v>
+      </c>
+      <c r="C11" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D11" t="str">
+        <v>题[q5] &gt;= 3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>支持来源不够稳定</v>
+      </c>
+      <c r="G11" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG_EV_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SG_AT_EXHAUST</v>
+      </c>
+      <c r="C12" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D12" t="str">
+        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>疲惫与意义感同时告急，是情绪耗竭的核心信号</v>
+      </c>
+      <c r="G12" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG_EV_21</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SG_AT_EFFICACY</v>
+      </c>
+      <c r="C13" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>维度[SG_EFFICACY] &gt;= 3.5</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>HERO 效能维度偏低</v>
+      </c>
+      <c r="G13" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG_EV_22</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SG_AT_EXHAUST</v>
+      </c>
+      <c r="C14" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="D14" t="str">
+        <v>维度[SG_RESILIENCE] &gt;= 3.5</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F14" t="str">
+        <v>HERO 韧性维度偏低，受挫后恢复困难</v>
+      </c>
+      <c r="G14" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SG_EV_23</v>
+      </c>
+      <c r="B15" t="str">
+        <v>SG_AT_MEANING</v>
+      </c>
+      <c r="C15" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="D15" t="str">
+        <v>维度[SG_HOPE] &gt;= 3.5</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2</v>
+      </c>
+      <c r="F15" t="str">
+        <v>HERO 希望维度偏低，看不到可行路径</v>
+      </c>
+      <c r="G15" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SG_EV_24</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SG_AT_MEANING</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="D16" t="str">
+        <v>维度[SG_OPTIMISM] &gt;= 3.5</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>HERO 乐观维度偏低</v>
+      </c>
+      <c r="G16" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>规则编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>所属模块*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码</v>
+      </c>
+      <c r="D1" t="str">
+        <v>优先级*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="F1" t="str">
+        <v>命中等级*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>等级中文名*</v>
+      </c>
+      <c r="H1" t="str">
+        <v>严重度*</v>
+      </c>
+      <c r="I1" t="str">
+        <v>是否红线熔断*</v>
+      </c>
+      <c r="J1" t="str">
+        <v>结果说明*</v>
+      </c>
+      <c r="K1" t="str">
+        <v>升级条件</v>
+      </c>
+      <c r="L1" t="str">
+        <v>升级目标</v>
+      </c>
+      <c r="M1" t="str">
+        <v>复评触发条件</v>
+      </c>
+      <c r="N1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SG_GRADE_PURPLE</v>
+      </c>
+      <c r="B2" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10</v>
+      </c>
+      <c r="E2" t="str">
+        <v>题[q3] &gt;= 4 且 题[q1] &gt;= 4</v>
+      </c>
+      <c r="F2" t="str">
+        <v>purple</v>
+      </c>
+      <c r="G2" t="str">
+        <v>需转介</v>
+      </c>
+      <c r="H2" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="I2" t="str">
+        <v>是</v>
+      </c>
+      <c r="J2" t="str">
+        <v>疲惫与意义感同时处于高位，已暂停常规建议并生成转介工单。</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>心理专员</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SG_GRADE_RED</v>
+      </c>
+      <c r="B3" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D3" t="str">
+        <v>20</v>
+      </c>
+      <c r="E3" t="str">
+        <v>状态总分 &gt;= 20</v>
+      </c>
+      <c r="F3" t="str">
+        <v>red</v>
+      </c>
+      <c r="G3" t="str">
+        <v>需关注</v>
+      </c>
+      <c r="H3" t="str">
+        <v>high</v>
+      </c>
+      <c r="I3" t="str">
+        <v>否</v>
+      </c>
+      <c r="J3" t="str">
+        <v>多项指标处于高位，建议本周内安排一次支持性沟通。</v>
+      </c>
+      <c r="K3" t="str">
+        <v>连续两次红色</v>
+      </c>
+      <c r="L3" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M3" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N3" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SG_GRADE_ORANGE</v>
+      </c>
+      <c r="B4" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D4" t="str">
+        <v>30</v>
+      </c>
+      <c r="E4" t="str">
+        <v>状态总分 &gt;= 17</v>
+      </c>
+      <c r="F4" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G4" t="str">
+        <v>需支持</v>
+      </c>
+      <c r="H4" t="str">
+        <v>high</v>
+      </c>
+      <c r="I4" t="str">
+        <v>否</v>
+      </c>
+      <c r="J4" t="str">
+        <v>状态已进入需要主动支持的区间，建议减少非必要承接。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>连续两次橙色</v>
+      </c>
+      <c r="L4" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M4" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N4" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SG_GRADE_YELLOW</v>
+      </c>
+      <c r="B5" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C5" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D5" t="str">
+        <v>40</v>
+      </c>
+      <c r="E5" t="str">
+        <v>状态总分 &gt;= 13</v>
+      </c>
+      <c r="F5" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G5" t="str">
+        <v>关注</v>
+      </c>
+      <c r="H5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I5" t="str">
+        <v>否</v>
+      </c>
+      <c r="J5" t="str">
+        <v>出现需要关注的波动，建议做针对性调整。</v>
+      </c>
+      <c r="K5" t="str">
+        <v>连续两次黄色</v>
+      </c>
+      <c r="L5" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M5" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N5" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SG_GRADE_BLUE</v>
+      </c>
+      <c r="B6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="D6" t="str">
+        <v>50</v>
+      </c>
+      <c r="E6" t="str">
+        <v>状态总分 &gt;= 10</v>
+      </c>
+      <c r="F6" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G6" t="str">
+        <v>轻微波动</v>
+      </c>
+      <c r="H6" t="str">
+        <v>low</v>
+      </c>
+      <c r="I6" t="str">
+        <v>否</v>
+      </c>
+      <c r="J6" t="str">
+        <v>存在轻微波动，保持现有节奏并留意变化即可。</v>
+      </c>
+      <c r="K6" t="str">
+        <v>复评转为黄色或以上</v>
+      </c>
+      <c r="L6" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M6" t="str">
+        <v>90天后复评</v>
+      </c>
+      <c r="N6" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SG_GRADE_GREEN</v>
+      </c>
+      <c r="B7" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>999</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>green</v>
+      </c>
+      <c r="G7" t="str">
+        <v>状态良好</v>
+      </c>
+      <c r="H7" t="str">
+        <v>low</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>当前状态整体稳定，保持现有节奏。</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
@@ -847,10 +1398,10 @@
         <v>self_growth</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>疲惫与意义感同时告急，属自我成长赋能模块红线</v>
+        <v>疲惫与意义感双双触顶，属自我成长模块红线</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -859,7 +1410,7 @@
         <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>1. 停止当前评估流程 2. 展示危机求助指引 3. 自动创建安全事件 4. 生成转介工单 5. 发送短信通知心理专员</v>
+        <v>停止当前评估流程,展示危机求助指引,创建安全事件,生成转介工单,短信通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>
@@ -868,10 +1419,10 @@
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在自我成长赋能评估中触发红线：疲惫与意义感同时告急。请尽快登录系统查看工单。</v>
+        <v>[教师姓名]老师在自我成长评估中触发红线：疲惫与意义感同时告急。请尽快登录系统查看工单。</v>
       </c>
       <c r="J2" t="str">
-        <v>PRD 8.3</v>
+        <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/self_growth/attribution.xlsx
+++ b/business-libraries/test-data/self_growth/attribution.xlsx
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1308,51 +1308,183 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_GRADE_GREEN</v>
+        <v>SG_GRADE_DEEP_RED</v>
       </c>
       <c r="B7" t="str">
         <v>self_growth</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D7" t="str">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F7" t="str">
-        <v>green</v>
+        <v>red</v>
       </c>
       <c r="G7" t="str">
-        <v>状态良好</v>
+        <v>需关注</v>
       </c>
       <c r="H7" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
       </c>
       <c r="J7" t="str">
+        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
+      </c>
+      <c r="K7" t="str">
+        <v>连续两次深评仍为红色</v>
+      </c>
+      <c r="L7" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M7" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N7" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG_GRADE_DEEP_YELLOW</v>
+      </c>
+      <c r="B8" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="D8" t="str">
+        <v>25</v>
+      </c>
+      <c r="E8" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G8" t="str">
+        <v>关注</v>
+      </c>
+      <c r="H8" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I8" t="str">
+        <v>否</v>
+      </c>
+      <c r="J8" t="str">
+        <v>心理资本出现波动，建议做针对性调整。</v>
+      </c>
+      <c r="K8" t="str">
+        <v>连续两次深评均分未下降</v>
+      </c>
+      <c r="L8" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M8" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N8" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG_GRADE_DEEP_BLUE</v>
+      </c>
+      <c r="B9" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C9" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="D9" t="str">
+        <v>35</v>
+      </c>
+      <c r="E9" t="str">
+        <v>均分 &gt;= 2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G9" t="str">
+        <v>轻微波动</v>
+      </c>
+      <c r="H9" t="str">
+        <v>low</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
+        <v>心理资本整体尚可，留意变化即可。</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG_GRADE_GREEN</v>
+      </c>
+      <c r="B10" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>999</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>green</v>
+      </c>
+      <c r="G10" t="str">
+        <v>状态良好</v>
+      </c>
+      <c r="H10" t="str">
+        <v>low</v>
+      </c>
+      <c r="I10" t="str">
+        <v>否</v>
+      </c>
+      <c r="J10" t="str">
         <v>当前状态整体稳定，保持现有节奏。</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L7" t="str">
+      <c r="L10" t="str">
         <v/>
       </c>
-      <c r="M7" t="str">
+      <c r="M10" t="str">
         <v/>
       </c>
-      <c r="N7" t="str">
+      <c r="N10" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N10"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/self_growth/attribution.xlsx
+++ b/business-libraries/test-data/self_growth/attribution.xlsx
@@ -437,13 +437,13 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>状态五问总分，反向题已折算</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="F2" t="str">
-        <v>q1-q5</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>情绪耗竭</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="B3" t="str">
         <v>角色边界失守</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="B4" t="str">
         <v>意义感流失</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>效能感不足</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>支持系统缺失</v>
@@ -691,10 +691,10 @@
         <v>SG_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D2" t="str">
         <v>题[q1] &gt;= 4</v>
@@ -714,10 +714,10 @@
         <v>SG_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D3" t="str">
         <v>题[q1] &gt;= 3</v>
@@ -737,10 +737,10 @@
         <v>SG_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D4" t="str">
         <v>题[q2] &gt;= 4</v>
@@ -760,10 +760,10 @@
         <v>SG_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D5" t="str">
         <v>题[q2] &gt;= 3</v>
@@ -783,10 +783,10 @@
         <v>SG_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D6" t="str">
         <v>题[q3] &gt;= 4</v>
@@ -806,10 +806,10 @@
         <v>SG_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D7" t="str">
         <v>题[q3] &gt;= 3</v>
@@ -829,10 +829,10 @@
         <v>SG_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D8" t="str">
         <v>题[q4] &gt;= 4</v>
@@ -852,10 +852,10 @@
         <v>SG_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D9" t="str">
         <v>题[q4] &gt;= 3</v>
@@ -875,10 +875,10 @@
         <v>SG_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D10" t="str">
         <v>题[q5] &gt;= 4</v>
@@ -898,10 +898,10 @@
         <v>SG_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D11" t="str">
         <v>题[q5] &gt;= 3</v>
@@ -921,10 +921,10 @@
         <v>SG_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C12" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D12" t="str">
         <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_EV_21</v>
+        <v>SG_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C13" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SG_EFFICACY] &gt;= 3.5</v>
+        <v>维度[SG_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E13" t="str">
         <v>2.5</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_EV_22</v>
+        <v>SG_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C14" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SG_RESILIENCE] &gt;= 3.5</v>
+        <v>维度[SG_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SG_EV_23</v>
+        <v>SG_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C15" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SG_HOPE] &gt;= 3.5</v>
+        <v>维度[SG_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SG_EV_24</v>
+        <v>SG_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C16" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SG_OPTIMISM] &gt;= 3.5</v>
+        <v>维度[SG_S2D4] &gt;= 3.5</v>
       </c>
       <c r="E16" t="str">
         <v>1.5</v>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1088,22 +1088,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_GRADE_PURPLE</v>
+        <v>SG_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
       </c>
       <c r="C2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q3] &gt;= 4 且 题[q1] &gt;= 4</v>
+        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>purple</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
         <v>需转介</v>
@@ -1132,22 +1132,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_GRADE_RED</v>
+        <v>SG_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S2</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>状态总分 &gt;= 20</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F3" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
         <v>需关注</v>
@@ -1159,10 +1159,10 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>多项指标处于高位，建议本周内安排一次支持性沟通。</v>
+        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次红色</v>
+        <v>连续两次深评仍为红色</v>
       </c>
       <c r="L3" t="str">
         <v>年级组长</v>
@@ -1176,37 +1176,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_GRADE_ORANGE</v>
+        <v>SG_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>self_growth</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S2</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>状态总分 &gt;= 17</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F4" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>需支持</v>
+        <v>关注</v>
       </c>
       <c r="H4" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>状态已进入需要主动支持的区间，建议减少非必要承接。</v>
+        <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次橙色</v>
+        <v>连续两次深评均分未下降</v>
       </c>
       <c r="L4" t="str">
         <v>年级组长</v>
@@ -1220,43 +1220,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_GRADE_YELLOW</v>
+        <v>SG_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>40</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>状态总分 &gt;= 13</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
-        <v>关注</v>
+        <v>需关注</v>
       </c>
       <c r="H5" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>出现需要关注的波动，建议做针对性调整。</v>
+        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次黄色</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v>自我成长赋能手册v1</v>
@@ -1264,43 +1264,43 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_GRADE_BLUE</v>
+        <v>SG_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>self_growth</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>50</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v>状态总分 &gt;= 10</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>blue</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>轻微波动</v>
+        <v>关注</v>
       </c>
       <c r="H6" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>存在轻微波动，保持现有节奏并留意变化即可。</v>
+        <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K6" t="str">
-        <v>复评转为黄色或以上</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>90天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v>自我成长赋能手册v1</v>
@@ -1308,22 +1308,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_GRADE_DEEP_RED</v>
+        <v>SG_GR_AUTO_03</v>
       </c>
       <c r="B7" t="str">
         <v>self_growth</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S3</v>
       </c>
       <c r="D7" t="str">
-        <v>15</v>
+        <v>503</v>
       </c>
       <c r="E7" t="str">
         <v>均分 &gt;= 4</v>
       </c>
       <c r="F7" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="G7" t="str">
         <v>需关注</v>
@@ -1338,13 +1338,13 @@
         <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K7" t="str">
-        <v>连续两次深评仍为红色</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N7" t="str">
         <v>自我成长赋能手册v1</v>
@@ -1352,19 +1352,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_GRADE_DEEP_YELLOW</v>
+        <v>SG_GR_AUTO_04</v>
       </c>
       <c r="B8" t="str">
         <v>self_growth</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S3</v>
       </c>
       <c r="D8" t="str">
-        <v>25</v>
+        <v>504</v>
       </c>
       <c r="E8" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F8" t="str">
         <v>yellow</v>
@@ -1382,13 +1382,13 @@
         <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K8" t="str">
-        <v>连续两次深评均分未下降</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N8" t="str">
         <v>自我成长赋能手册v1</v>
@@ -1396,25 +1396,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_GRADE_DEEP_BLUE</v>
+        <v>SG_GR_DEFAULT</v>
       </c>
       <c r="B9" t="str">
         <v>self_growth</v>
       </c>
       <c r="C9" t="str">
-        <v>SG_HERO_AS</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>35</v>
+        <v>999</v>
       </c>
       <c r="E9" t="str">
-        <v>均分 &gt;= 2</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>blue</v>
+        <v>green</v>
       </c>
       <c r="G9" t="str">
-        <v>轻微波动</v>
+        <v>状态良好</v>
       </c>
       <c r="H9" t="str">
         <v>low</v>
@@ -1423,7 +1423,7 @@
         <v>否</v>
       </c>
       <c r="J9" t="str">
-        <v>心理资本整体尚可，留意变化即可。</v>
+        <v>本次评估未发现需要重点干预的信号</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1435,56 +1435,12 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>SG_GRADE_GREEN</v>
-      </c>
-      <c r="B10" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>999</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>green</v>
-      </c>
-      <c r="G10" t="str">
-        <v>状态良好</v>
-      </c>
-      <c r="H10" t="str">
-        <v>low</v>
-      </c>
-      <c r="I10" t="str">
-        <v>否</v>
-      </c>
-      <c r="J10" t="str">
-        <v>当前状态整体稳定，保持现有节奏。</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1530,10 +1486,10 @@
         <v>self_growth</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 5</v>
+        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 4</v>
       </c>
       <c r="C2" t="str">
-        <v>疲惫与意义感双双触顶，属自我成长模块红线</v>
+        <v>疲惫与意义感同时处于高位，已暂停常规建议并生成转介工单。</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1542,7 +1498,7 @@
         <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止当前评估流程,展示危机求助指引,创建安全事件,生成转介工单,短信通知心理专员</v>
+        <v>停止当前评估流程；展示危机求助指引；创建安全事件；生成转介工单；短信通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>

--- a/business-libraries/test-data/self_growth/attribution.xlsx
+++ b/business-libraries/test-data/self_growth/attribution.xlsx
@@ -437,13 +437,13 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>状态五问总分，反向题已折算</v>
       </c>
       <c r="E2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>q1-q5</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="B2" t="str">
         <v>情绪耗竭</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_AT_02</v>
+        <v>SG_AT_BOUNDARY</v>
       </c>
       <c r="B3" t="str">
         <v>角色边界失守</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="B4" t="str">
         <v>意义感流失</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_EFFICACY</v>
       </c>
       <c r="B5" t="str">
         <v>效能感不足</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_AT_05</v>
+        <v>SG_AT_SUPPORT</v>
       </c>
       <c r="B6" t="str">
         <v>支持系统缺失</v>
@@ -691,10 +691,10 @@
         <v>SG_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="C2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D2" t="str">
         <v>题[q1] &gt;= 4</v>
@@ -714,10 +714,10 @@
         <v>SG_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D3" t="str">
         <v>题[q1] &gt;= 3</v>
@@ -737,10 +737,10 @@
         <v>SG_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_AT_02</v>
+        <v>SG_AT_BOUNDARY</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D4" t="str">
         <v>题[q2] &gt;= 4</v>
@@ -760,10 +760,10 @@
         <v>SG_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_AT_02</v>
+        <v>SG_AT_BOUNDARY</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D5" t="str">
         <v>题[q2] &gt;= 3</v>
@@ -783,10 +783,10 @@
         <v>SG_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D6" t="str">
         <v>题[q3] &gt;= 4</v>
@@ -806,10 +806,10 @@
         <v>SG_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D7" t="str">
         <v>题[q3] &gt;= 3</v>
@@ -829,10 +829,10 @@
         <v>SG_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_EFFICACY</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D8" t="str">
         <v>题[q4] &gt;= 4</v>
@@ -852,10 +852,10 @@
         <v>SG_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_EFFICACY</v>
       </c>
       <c r="C9" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D9" t="str">
         <v>题[q4] &gt;= 3</v>
@@ -875,10 +875,10 @@
         <v>SG_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_AT_05</v>
+        <v>SG_AT_SUPPORT</v>
       </c>
       <c r="C10" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D10" t="str">
         <v>题[q5] &gt;= 4</v>
@@ -898,10 +898,10 @@
         <v>SG_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SG_AT_05</v>
+        <v>SG_AT_SUPPORT</v>
       </c>
       <c r="C11" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D11" t="str">
         <v>题[q5] &gt;= 3</v>
@@ -921,10 +921,10 @@
         <v>SG_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="C12" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D12" t="str">
         <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_EV_12</v>
+        <v>SG_EV_21</v>
       </c>
       <c r="B13" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_EFFICACY</v>
       </c>
       <c r="C13" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SG_S2D2] &gt;= 3.5</v>
+        <v>维度[SG_EFFICACY] &gt;= 3.5</v>
       </c>
       <c r="E13" t="str">
         <v>2.5</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_EV_13</v>
+        <v>SG_EV_22</v>
       </c>
       <c r="B14" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="C14" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SG_S2D3] &gt;= 3.5</v>
+        <v>维度[SG_RESILIENCE] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SG_EV_14</v>
+        <v>SG_EV_23</v>
       </c>
       <c r="B15" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="C15" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SG_S2D1] &gt;= 3.5</v>
+        <v>维度[SG_HOPE] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SG_EV_15</v>
+        <v>SG_EV_24</v>
       </c>
       <c r="B16" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="C16" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SG_S2D4] &gt;= 3.5</v>
+        <v>维度[SG_OPTIMISM] &gt;= 3.5</v>
       </c>
       <c r="E16" t="str">
         <v>1.5</v>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:P10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1083,27 +1083,33 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_GR_01</v>
+        <v>SG_GRADE_PURPLE</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
       </c>
       <c r="C2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 4</v>
+        <v>题[q3] &gt;= 4 且 题[q1] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>purple</v>
       </c>
       <c r="G2" t="str">
         <v>需转介</v>
@@ -1127,27 +1133,33 @@
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_GR_02</v>
+        <v>SG_GRADE_RED</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_S2</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>状态总分 &gt;= 20</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>red</v>
       </c>
       <c r="G3" t="str">
         <v>需关注</v>
@@ -1159,10 +1171,10 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
+        <v>多项指标处于高位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次深评仍为红色</v>
+        <v>连续两次红色</v>
       </c>
       <c r="L3" t="str">
         <v>年级组长</v>
@@ -1171,42 +1183,48 @@
         <v>14天后复评</v>
       </c>
       <c r="N3" t="str">
+        <v>SG_RX_001</v>
+      </c>
+      <c r="O3" t="str">
+        <v>本周内完成一次支持性沟通并记录反馈。</v>
+      </c>
+      <c r="P3" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_GR_03</v>
+        <v>SG_GRADE_ORANGE</v>
       </c>
       <c r="B4" t="str">
         <v>self_growth</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_S2</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>状态总分 &gt;= 17</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="G4" t="str">
-        <v>关注</v>
+        <v>需支持</v>
       </c>
       <c r="H4" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>心理资本出现波动，建议做针对性调整。</v>
+        <v>状态已进入需要主动支持的区间，建议减少非必要承接。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次深评均分未下降</v>
+        <v>连续两次橙色</v>
       </c>
       <c r="L4" t="str">
         <v>年级组长</v>
@@ -1215,115 +1233,133 @@
         <v>30天后复评</v>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_GR_AUTO_01</v>
+        <v>SG_GRADE_YELLOW</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>状态总分 &gt;= 13</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="G5" t="str">
-        <v>需关注</v>
+        <v>关注</v>
       </c>
       <c r="H5" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
+        <v>出现需要关注的波动，建议做针对性调整。</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>连续两次黄色</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>30天后复评</v>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_GR_AUTO_02</v>
+        <v>SG_GRADE_BLUE</v>
       </c>
       <c r="B6" t="str">
         <v>self_growth</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>50</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>状态总分 &gt;= 10</v>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>blue</v>
       </c>
       <c r="G6" t="str">
-        <v>关注</v>
+        <v>轻微波动</v>
       </c>
       <c r="H6" t="str">
-        <v>medium</v>
+        <v>low</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>心理资本出现波动，建议做针对性调整。</v>
+        <v>存在轻微波动，保持现有节奏并留意变化即可。</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>复评转为黄色或以上</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>90天后复评</v>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_GR_AUTO_03</v>
+        <v>SG_GRADE_DEEP_RED</v>
       </c>
       <c r="B7" t="str">
         <v>self_growth</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_S3</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D7" t="str">
-        <v>503</v>
+        <v>15</v>
       </c>
       <c r="E7" t="str">
         <v>均分 &gt;= 4</v>
       </c>
       <c r="F7" t="str">
-        <v>orange</v>
+        <v>red</v>
       </c>
       <c r="G7" t="str">
         <v>需关注</v>
@@ -1338,33 +1374,39 @@
         <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>连续两次深评仍为红色</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>14天后复评</v>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_GR_AUTO_04</v>
+        <v>SG_GRADE_DEEP_YELLOW</v>
       </c>
       <c r="B8" t="str">
         <v>self_growth</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_S3</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D8" t="str">
-        <v>504</v>
+        <v>25</v>
       </c>
       <c r="E8" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F8" t="str">
         <v>yellow</v>
@@ -1382,39 +1424,45 @@
         <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>连续两次深评均分未下降</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>30天后复评</v>
       </c>
       <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_GR_DEFAULT</v>
+        <v>SG_GRADE_DEEP_BLUE</v>
       </c>
       <c r="B9" t="str">
         <v>self_growth</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="D9" t="str">
-        <v>999</v>
+        <v>35</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>均分 &gt;= 2</v>
       </c>
       <c r="F9" t="str">
-        <v>green</v>
+        <v>blue</v>
       </c>
       <c r="G9" t="str">
-        <v>状态良好</v>
+        <v>轻微波动</v>
       </c>
       <c r="H9" t="str">
         <v>low</v>
@@ -1423,7 +1471,7 @@
         <v>否</v>
       </c>
       <c r="J9" t="str">
-        <v>本次评估未发现需要重点干预的信号</v>
+        <v>心理资本整体尚可，留意变化即可。</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1435,12 +1483,68 @@
         <v/>
       </c>
       <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG_GRADE_GREEN</v>
+      </c>
+      <c r="B10" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>999</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>green</v>
+      </c>
+      <c r="G10" t="str">
+        <v>状态良好</v>
+      </c>
+      <c r="H10" t="str">
+        <v>low</v>
+      </c>
+      <c r="I10" t="str">
+        <v>否</v>
+      </c>
+      <c r="J10" t="str">
+        <v>当前状态整体稳定，保持现有节奏。</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1486,10 +1590,10 @@
         <v>self_growth</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 4</v>
+        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>疲惫与意义感同时处于高位，已暂停常规建议并生成转介工单。</v>
+        <v>疲惫与意义感双双触顶，属自我成长模块红线</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1498,7 +1602,7 @@
         <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止当前评估流程；展示危机求助指引；创建安全事件；生成转介工单；短信通知心理专员</v>
+        <v>停止当前评估流程,展示危机求助指引,创建安全事件,生成转介工单,短信通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>

--- a/business-libraries/test-data/self_growth/attribution.xlsx
+++ b/business-libraries/test-data/self_growth/attribution.xlsx
@@ -437,13 +437,13 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>状态五问总分，反向题已折算</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="F2" t="str">
-        <v>q1-q5</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>情绪耗竭</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="B3" t="str">
         <v>角色边界失守</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="B4" t="str">
         <v>意义感流失</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>效能感不足</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>支持系统缺失</v>
@@ -691,10 +691,10 @@
         <v>SG_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D2" t="str">
         <v>题[q1] &gt;= 4</v>
@@ -714,10 +714,10 @@
         <v>SG_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D3" t="str">
         <v>题[q1] &gt;= 3</v>
@@ -737,10 +737,10 @@
         <v>SG_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D4" t="str">
         <v>题[q2] &gt;= 4</v>
@@ -760,10 +760,10 @@
         <v>SG_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D5" t="str">
         <v>题[q2] &gt;= 3</v>
@@ -783,10 +783,10 @@
         <v>SG_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D6" t="str">
         <v>题[q3] &gt;= 4</v>
@@ -806,10 +806,10 @@
         <v>SG_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D7" t="str">
         <v>题[q3] &gt;= 3</v>
@@ -829,10 +829,10 @@
         <v>SG_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D8" t="str">
         <v>题[q4] &gt;= 4</v>
@@ -852,10 +852,10 @@
         <v>SG_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D9" t="str">
         <v>题[q4] &gt;= 3</v>
@@ -875,10 +875,10 @@
         <v>SG_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D10" t="str">
         <v>题[q5] &gt;= 4</v>
@@ -898,10 +898,10 @@
         <v>SG_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D11" t="str">
         <v>题[q5] &gt;= 3</v>
@@ -921,10 +921,10 @@
         <v>SG_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C12" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D12" t="str">
         <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_EV_21</v>
+        <v>SG_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C13" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SG_EFFICACY] &gt;= 3.5</v>
+        <v>维度[SG_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E13" t="str">
         <v>2.5</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_EV_22</v>
+        <v>SG_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="C14" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SG_RESILIENCE] &gt;= 3.5</v>
+        <v>维度[SG_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SG_EV_23</v>
+        <v>SG_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C15" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SG_HOPE] &gt;= 3.5</v>
+        <v>维度[SG_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SG_EV_24</v>
+        <v>SG_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C16" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SG_OPTIMISM] &gt;= 3.5</v>
+        <v>维度[SG_S2D4] &gt;= 3.5</v>
       </c>
       <c r="E16" t="str">
         <v>1.5</v>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1094,22 +1094,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_GRADE_PURPLE</v>
+        <v>SG_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>self_growth</v>
       </c>
       <c r="C2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q3] &gt;= 4 且 题[q1] &gt;= 4</v>
+        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>purple</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
         <v>需转介</v>
@@ -1144,22 +1144,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_GRADE_RED</v>
+        <v>SG_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S2</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>状态总分 &gt;= 20</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F3" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
         <v>需关注</v>
@@ -1171,10 +1171,10 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>多项指标处于高位，建议本周内安排一次支持性沟通。</v>
+        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次红色</v>
+        <v>连续两次深评仍为红色</v>
       </c>
       <c r="L3" t="str">
         <v>年级组长</v>
@@ -1183,10 +1183,10 @@
         <v>14天后复评</v>
       </c>
       <c r="N3" t="str">
-        <v>SG_RX_001</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v>本周内完成一次支持性沟通并记录反馈。</v>
+        <v/>
       </c>
       <c r="P3" t="str">
         <v>自我成长赋能手册v1</v>
@@ -1194,37 +1194,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_GRADE_ORANGE</v>
+        <v>SG_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>self_growth</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S2</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>状态总分 &gt;= 17</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F4" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>需支持</v>
+        <v>关注</v>
       </c>
       <c r="H4" t="str">
-        <v>high</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>状态已进入需要主动支持的区间，建议减少非必要承接。</v>
+        <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K4" t="str">
-        <v>连续两次橙色</v>
+        <v>连续两次深评均分未下降</v>
       </c>
       <c r="L4" t="str">
         <v>年级组长</v>
@@ -1244,43 +1244,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_GRADE_YELLOW</v>
+        <v>SG_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>40</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>状态总分 &gt;= 13</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
-        <v>关注</v>
+        <v>需关注</v>
       </c>
       <c r="H5" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>出现需要关注的波动，建议做针对性调整。</v>
+        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次黄色</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -1294,43 +1294,43 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_GRADE_BLUE</v>
+        <v>SG_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>self_growth</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>50</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v>状态总分 &gt;= 10</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>blue</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>轻微波动</v>
+        <v>关注</v>
       </c>
       <c r="H6" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>存在轻微波动，保持现有节奏并留意变化即可。</v>
+        <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K6" t="str">
-        <v>复评转为黄色或以上</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>90天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -1344,22 +1344,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_GRADE_DEEP_RED</v>
+        <v>SG_GR_AUTO_03</v>
       </c>
       <c r="B7" t="str">
         <v>self_growth</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S3</v>
       </c>
       <c r="D7" t="str">
-        <v>15</v>
+        <v>503</v>
       </c>
       <c r="E7" t="str">
         <v>均分 &gt;= 4</v>
       </c>
       <c r="F7" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="G7" t="str">
         <v>需关注</v>
@@ -1374,13 +1374,13 @@
         <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
       </c>
       <c r="K7" t="str">
-        <v>连续两次深评仍为红色</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -1394,19 +1394,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_GRADE_DEEP_YELLOW</v>
+        <v>SG_GR_AUTO_04</v>
       </c>
       <c r="B8" t="str">
         <v>self_growth</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S3</v>
       </c>
       <c r="D8" t="str">
-        <v>25</v>
+        <v>504</v>
       </c>
       <c r="E8" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F8" t="str">
         <v>yellow</v>
@@ -1424,13 +1424,13 @@
         <v>心理资本出现波动，建议做针对性调整。</v>
       </c>
       <c r="K8" t="str">
-        <v>连续两次深评均分未下降</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -1444,25 +1444,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_GRADE_DEEP_BLUE</v>
+        <v>SG_GR_DEFAULT</v>
       </c>
       <c r="B9" t="str">
         <v>self_growth</v>
       </c>
       <c r="C9" t="str">
-        <v>SG_HERO_AS</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>35</v>
+        <v>999</v>
       </c>
       <c r="E9" t="str">
-        <v>均分 &gt;= 2</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>blue</v>
+        <v>green</v>
       </c>
       <c r="G9" t="str">
-        <v>轻微波动</v>
+        <v>状态良好</v>
       </c>
       <c r="H9" t="str">
         <v>low</v>
@@ -1471,7 +1471,7 @@
         <v>否</v>
       </c>
       <c r="J9" t="str">
-        <v>心理资本整体尚可，留意变化即可。</v>
+        <v>本次评估未发现需要重点干预的信号</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1489,62 +1489,12 @@
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>SG_GRADE_GREEN</v>
-      </c>
-      <c r="B10" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>999</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>green</v>
-      </c>
-      <c r="G10" t="str">
-        <v>状态良好</v>
-      </c>
-      <c r="H10" t="str">
-        <v>low</v>
-      </c>
-      <c r="I10" t="str">
-        <v>否</v>
-      </c>
-      <c r="J10" t="str">
-        <v>当前状态整体稳定，保持现有节奏。</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1590,10 +1540,10 @@
         <v>self_growth</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 5</v>
+        <v>量表[SG_S1].题[q1] &gt;= 5 且 量表[SG_S1].题[q3] &gt;= 4</v>
       </c>
       <c r="C2" t="str">
-        <v>疲惫与意义感双双触顶，属自我成长模块红线</v>
+        <v>疲惫与意义感同时处于高位，已暂停常规建议并生成转介工单。</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1602,7 +1552,7 @@
         <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止当前评估流程,展示危机求助指引,创建安全事件,生成转介工单,短信通知心理专员</v>
+        <v>停止当前评估流程；展示危机求助指引；创建安全事件；生成转介工单；短信通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>

--- a/business-libraries/test-data/self_growth/attribution.xlsx
+++ b/business-libraries/test-data/self_growth/attribution.xlsx
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -506,7 +506,7 @@
         <v>1.3</v>
       </c>
       <c r="E2" t="str">
-        <v>self_growth,emotion,pressure</v>
+        <v>self_growth,emotion,burnout</v>
       </c>
       <c r="F2" t="str">
         <v>教师的情绪资源被持续消耗且难以自然恢复，是职业倦怠的核心成分。</v>
@@ -521,7 +521,7 @@
         <v>本周内安排两段各 30 分钟的不可打扰恢复时段，并减少一项非必要班务承接</v>
       </c>
       <c r="J2" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +529,7 @@
         <v>SG_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>角色边界失守</v>
+        <v>精力耗尽与躯体疲劳</v>
       </c>
       <c r="C3" t="str">
         <v>self_growth</v>
@@ -538,22 +538,22 @@
         <v>1.1</v>
       </c>
       <c r="E3" t="str">
-        <v>self_growth,boundary</v>
+        <v>self_growth,body,fatigue</v>
       </c>
       <c r="F3" t="str">
-        <v>教师把超出职责范围的责任持续揽在自己身上，导致负荷不可控。</v>
+        <v>身体能量长期透支，陷入疲劳-低效循环，出现躯体化压力反应。</v>
       </c>
       <c r="G3" t="str">
-        <v>认为「什么都是我的责任」、难以拒绝额外要求、下班后仍在处理班务</v>
+        <v>下午极度疲劳、肩颈酸痛、全身紧绷、久坐后注意力断崖式下降</v>
       </c>
       <c r="H3" t="str">
-        <v>学校分工不清或教师自我期待过高</v>
+        <v>连续工作超 3 小时无休息、久坐不动、咖啡因替代休息</v>
       </c>
       <c r="I3" t="str">
-        <v>做一次职责边界盘点，把当前压力拆成可控制、可影响、暂时不可控三类，只推进可控的一项</v>
+        <v>每小时起身活动 2-3 分钟，每天安排一次身体放松练习（渐进式肌肉放松或身体扫描）</v>
       </c>
       <c r="J3" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -561,31 +561,31 @@
         <v>SG_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>意义感流失</v>
+        <v>睡眠问题</v>
       </c>
       <c r="C4" t="str">
         <v>self_growth</v>
       </c>
       <c r="D4" t="str">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="str">
-        <v>self_growth,meaning</v>
+        <v>self_growth,body,sleep</v>
       </c>
       <c r="F4" t="str">
-        <v>教师对班主任工作的价值感知下降，是需要重点关注的信号。</v>
+        <v>入睡困难、睡眠质量差、早晨疲惫，是情绪耗竭最先反映的客观指标。</v>
       </c>
       <c r="G4" t="str">
-        <v>反复怀疑工作的价值、对学生的进步不再有反应</v>
+        <v>入睡超过 30 分钟、夜间易醒早醒、白天疲惫</v>
       </c>
       <c r="H4" t="str">
-        <v>长期付出未获反馈，或经历重大挫败事件</v>
+        <v>睡前处理工作、屏幕蓝光暴露、大脑停不下来</v>
       </c>
       <c r="I4" t="str">
-        <v>记录一件本周确实因为你而变好的小事，并找一位同伴讲给他听</v>
+        <v>执行睡前数字日落流程：睡前 1 小时放下屏幕，做脑力倾倒与放松练习</v>
       </c>
       <c r="J4" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +593,7 @@
         <v>SG_AT_04</v>
       </c>
       <c r="B5" t="str">
-        <v>效能感不足</v>
+        <v>急性焦虑与紧张</v>
       </c>
       <c r="C5" t="str">
         <v>self_growth</v>
@@ -602,22 +602,22 @@
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>self_growth,efficacy</v>
+        <v>self_growth,emotion,anxiety</v>
       </c>
       <c r="F5" t="str">
-        <v>教师对自己处理复杂问题的能力缺乏信心，容易回避而非应对。</v>
+        <v>面对棘手情境时的急性焦虑反应，干扰理性思考与临场表现。</v>
       </c>
       <c r="G5" t="str">
-        <v>遇到难题先想到「我搞不定」、倾向于上交问题</v>
+        <v>心跳加速、大脑空白、紧张到无法行动</v>
       </c>
       <c r="H5" t="str">
-        <v>缺少可复用的方法储备或成功经验</v>
+        <v>重要事件前、突发冲突、被投诉被质疑时</v>
       </c>
       <c r="I5" t="str">
-        <v>选一个最小的难题，用一个具体工具完整走一遍并记录结果</v>
+        <v>用 478 呼吸法 30 秒降心率、激活副交感神经，冷静后再处理事件</v>
       </c>
       <c r="J5" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -625,43 +625,875 @@
         <v>SG_AT_05</v>
       </c>
       <c r="B6" t="str">
+        <v>灾难化思维</v>
+      </c>
+      <c r="C6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>self_growth,cognition,anxiety</v>
+      </c>
+      <c r="F6" t="str">
+        <v>过度放大最坏情况的心理偏差，焦虑阻碍行动形成回避循环。</v>
+      </c>
+      <c r="G6" t="str">
+        <v>脑中不断预演最坏场景、过度担心、不敢行动</v>
+      </c>
+      <c r="H6" t="str">
+        <v>结果不确定的重要事项、缺乏应对预案</v>
+      </c>
+      <c r="I6" t="str">
+        <v>做最坏情况预演：写下最坏结果、应对措施与可求助资源，再行动</v>
+      </c>
+      <c r="J6" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SG_AT_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>情绪觉察薄弱</v>
+      </c>
+      <c r="C7" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>self_growth,emotion,awareness</v>
+      </c>
+      <c r="F7" t="str">
+        <v>说不清自己的情绪状态，情绪累积到临界点才突然爆发。</v>
+      </c>
+      <c r="G7" t="str">
+        <v>突然爆发吓到自己和他人、用「烦/累」模糊概括所有情绪</v>
+      </c>
+      <c r="H7" t="str">
+        <v>长期忽略微小情绪信号、没有情绪记录习惯</v>
+      </c>
+      <c r="I7" t="str">
+        <v>用情绪温度计每天 3 次自评（黄灯即处理），配合情绪命名练习提升情绪粒度</v>
+      </c>
+      <c r="J7" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG_AT_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>情绪劳动耗竭</v>
+      </c>
+      <c r="C8" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D8" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E8" t="str">
+        <v>self_growth,emotion,burnout</v>
+      </c>
+      <c r="F8" t="str">
+        <v>浅层扮演（装）的长期内耗导致内外割裂，是班主任困境核心机制之一。</v>
+      </c>
+      <c r="G8" t="str">
+        <v>人前温暖独处崩溃、下班后情绪爆发、维持多个情绪面具</v>
+      </c>
+      <c r="H8" t="str">
+        <v>必须维持「亲切耐心」形象、浅层扮演持续超过 2 周</v>
+      </c>
+      <c r="I8" t="str">
+        <v>用情绪充电站四步（深呼吸→命名情绪→允许存在→选择回应）从浅层扮演转向深层扮演</v>
+      </c>
+      <c r="J8" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG_AT_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>共情疲劳</v>
+      </c>
+      <c r="C9" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E9" t="str">
+        <v>self_growth,emotion,fatigue</v>
+      </c>
+      <c r="F9" t="str">
+        <v>长期接触学生痛苦情绪导致情绪资源耗竭，96.71% 班主任存在不同程度共情疲劳。</v>
+      </c>
+      <c r="G9" t="str">
+        <v>对学生情绪反应范围收窄、不愿情感深入、对学生问题麻木</v>
+      </c>
+      <c r="H9" t="str">
+        <v>每天承接几十个孩子的情绪需求、不安全依恋调节策略脆弱</v>
+      </c>
+      <c r="I9" t="str">
+        <v>每月做共情检查站自检，识别到耗竭及时补能，必要时寻求支持</v>
+      </c>
+      <c r="J9" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG_AT_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>双重依恋困境</v>
+      </c>
+      <c r="C10" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D10" t="str">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>self_growth,relation,attachment</v>
+      </c>
+      <c r="F10" t="str">
+        <v>小学班主任特有消耗机制：学生的依恋需求反复激活教师自身依恋系统，依恋安全感不足时形成负循环。</v>
+      </c>
+      <c r="G10" t="str">
+        <v>过度卷入或情感回避交替出现、越回应越耗竭</v>
+      </c>
+      <c r="H10" t="str">
+        <v>6-12 岁学生高依恋需求+教师自身依恋安全感不足</v>
+      </c>
+      <c r="I10" t="str">
+        <v>先做 AS 快筛了解自己的调节模式，干预遵循依恋知情原则（先情感回应再给策略）</v>
+      </c>
+      <c r="J10" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG_AT_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>角色边界消失</v>
+      </c>
+      <c r="C11" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E11" t="str">
+        <v>self_growth,boundary</v>
+      </c>
+      <c r="F11" t="str">
+        <v>把学生的一切问题都当成自己的责任，边界消失，被需要=被肯定（A 过载-全能模式）。</v>
+      </c>
+      <c r="G11" t="str">
+        <v>「什么都是我的责任」、无法拒绝额外要求、下班后仍处理班务</v>
+      </c>
+      <c r="H11" t="str">
+        <v>学校分工不清或教师自我期待过高、被需要感驱动</v>
+      </c>
+      <c r="I11" t="str">
+        <v>做责任边界思维练习：把困扰事项分为责任圈/影响圈/他人系统责任，只推进可控的一项</v>
+      </c>
+      <c r="J11" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG_AT_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>边界感丧失</v>
+      </c>
+      <c r="C12" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>self_growth,boundary</v>
+      </c>
+      <c r="F12" t="str">
+        <v>时间、职责、情绪边界不断被突破，个人时间与精力被持续侵占。</v>
+      </c>
+      <c r="G12" t="str">
+        <v>家长随时联系、非工作时间被占用、不敢拒绝、答应了又后悔</v>
+      </c>
+      <c r="H12" t="str">
+        <v>未建立边界声明、拒绝困难、怕伤害关系</v>
+      </c>
+      <c r="I12" t="str">
+        <v>用边界声明话术与标准化拒绝模板建立并维护个人边界</v>
+      </c>
+      <c r="J12" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG_AT_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>完美主义</v>
+      </c>
+      <c r="C13" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D13" t="str">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>self_growth,cognition,perfectionism</v>
+      </c>
+      <c r="F13" t="str">
+        <v>反复打磨不敢交付，「够好」标准缺失，效率与心理双重受损。</v>
+      </c>
+      <c r="G13" t="str">
+        <v>反复修改检查犹豫、不敢开始、对「差不多」无法接受</v>
+      </c>
+      <c r="H13" t="str">
+        <v>高标准内化、害怕被评价、边际收益递减仍不放手</v>
+      </c>
+      <c r="I13" t="str">
+        <v>做完美主义去魅：设定 60/80/95 分三级标准，90% 的事做到 80 分即可</v>
+      </c>
+      <c r="J13" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG_AT_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>过度自责</v>
+      </c>
+      <c r="C14" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>self_growth,cognition</v>
+      </c>
+      <c r="F14" t="str">
+        <v>把所有问题都归因于自己能力不足，自我攻击加剧习得性无助。</v>
+      </c>
+      <c r="G14" t="str">
+        <v>「都是我的错」「我就是不行」、拒绝正面反馈</v>
+      </c>
+      <c r="H14" t="str">
+        <v>消极能力归因+高自我期待、失败经历累积</v>
+      </c>
+      <c r="I14" t="str">
+        <v>用归因重构三步法做归因三角检验，写下平衡归因陈述</v>
+      </c>
+      <c r="J14" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SG_AT_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>冒名顶替综合征</v>
+      </c>
+      <c r="C15" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D15" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>self_growth,cognition</v>
+      </c>
+      <c r="F15" t="str">
+        <v>明明有能力却感觉自己不配，被肯定归为运气，93% 以上职前教师存在冒名顶替想法。</v>
+      </c>
+      <c r="G15" t="str">
+        <v>被肯定归结为运气、无法内化成功、觉得随时会被发现「不配」</v>
+      </c>
+      <c r="H15" t="str">
+        <v>新手期、外部证据无法动摇其信念</v>
+      </c>
+      <c r="I15" t="str">
+        <v>用自戒暂停与「我的不可替代性」反思：自己列出 3 件 AI 无法替代的独特做法</v>
+      </c>
+      <c r="J15" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SG_AT_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>认知锁定</v>
+      </c>
+      <c r="C16" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E16" t="str">
+        <v>self_growth,cognition</v>
+      </c>
+      <c r="F16" t="str">
+        <v>消极归因→行为退缩→负性结果→强化消极归因的自我强化闭环，67.3% 班主任存在。</v>
+      </c>
+      <c r="G16" t="str">
+        <v>大量自我否定语言、拒绝正面反馈、回避尝试</v>
+      </c>
+      <c r="H16" t="str">
+        <v>失败经历重复+缺乏成功证据，冒名顶替加剧</v>
+      </c>
+      <c r="I16" t="str">
+        <v>用认知转换卡打开可变空间（「还」字法），配合进步证据库用微小成功逐步松动</v>
+      </c>
+      <c r="J16" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_AT_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>意义感流失</v>
+      </c>
+      <c r="C17" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D17" t="str">
+        <v>1.4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>self_growth,meaning</v>
+      </c>
+      <c r="F17" t="str">
+        <v>对班主任工作的价值感知下降，成就感延迟导致意义来源不足。</v>
+      </c>
+      <c r="G17" t="str">
+        <v>反复怀疑工作价值、对学生进步不再有反应、例行公事感</v>
+      </c>
+      <c r="H17" t="str">
+        <v>成就感延迟、长期付出未获反馈、成果难以量化</v>
+      </c>
+      <c r="I17" t="str">
+        <v>用影响力日志每周记录一件对学生的积极影响，配合教育初心回溯重建意义</v>
+      </c>
+      <c r="J17" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_AT_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>职业认同下降</v>
+      </c>
+      <c r="C18" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E18" t="str">
+        <v>self_growth,meaning,identity</v>
+      </c>
+      <c r="F18" t="str">
+        <v>对班主任职业的价值认同、归属感与发展意愿下降，职业认同&lt;2.5 分触发紫色（意义危机）预警。</v>
+      </c>
+      <c r="G18" t="str">
+        <v>觉得做这些没意思、只是为工资硬撑、找不到职业方向</v>
+      </c>
+      <c r="H18" t="str">
+        <v>价值冲突、长期无正向反馈、意义危机</v>
+      </c>
+      <c r="I18" t="str">
+        <v>通过职业认同量表确认后启动意义重构专项，探索职业意义锚点</v>
+      </c>
+      <c r="J18" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_AT_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>心理资本不足</v>
+      </c>
+      <c r="C19" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D19" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>self_growth,psychology</v>
+      </c>
+      <c r="F19" t="str">
+        <v>HERO 四维度（希望/效能/韧性/乐观）整体偏低，心理资本匮乏。</v>
+      </c>
+      <c r="G19" t="str">
+        <v>看不到可行路径、对未来消极预期、受挫后难以恢复</v>
+      </c>
+      <c r="H19" t="str">
+        <v>长期挫折+缺乏成功体验+支持不足</v>
+      </c>
+      <c r="I19" t="str">
+        <v>用微成功阶梯每天完成 3 个「微小到不可能失败」的任务，重建自我效能</v>
+      </c>
+      <c r="J19" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_AT_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>效能感不足</v>
+      </c>
+      <c r="C20" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D20" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>self_growth,psychology,efficacy</v>
+      </c>
+      <c r="F20" t="str">
+        <v>对自己处理复杂问题的能力缺乏信心，容易回避而非应对。</v>
+      </c>
+      <c r="G20" t="str">
+        <v>遇到难题先想「我搞不定」、倾向于上交问题</v>
+      </c>
+      <c r="H20" t="str">
+        <v>缺少可复用的方法储备或成功经验</v>
+      </c>
+      <c r="I20" t="str">
+        <v>用最小成功案例复演，把一次成功经验拆成三步套用到当前难题</v>
+      </c>
+      <c r="J20" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SG_AT_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>韧性不足</v>
+      </c>
+      <c r="C21" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D21" t="str">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>self_growth,psychology</v>
+      </c>
+      <c r="F21" t="str">
+        <v>受挫后长时间难以恢复，挫折持续影响生活与工作状态。</v>
+      </c>
+      <c r="G21" t="str">
+        <v>被批评后一蹶不振、挫折影响睡眠和生活</v>
+      </c>
+      <c r="H21" t="str">
+        <v>缺乏恢复资源与缓冲、情绪恢复路径缺失</v>
+      </c>
+      <c r="I21" t="str">
+        <v>用渐进式肌肉放松降低躯体紧张，配合同伴支持加速恢复</v>
+      </c>
+      <c r="J21" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SG_AT_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>基本心理需要受挫</v>
+      </c>
+      <c r="C22" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D22" t="str">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>self_growth,psychology</v>
+      </c>
+      <c r="F22" t="str">
+        <v>自主、能力、关系三大基本心理需要同时受压（SDT 理论），是倦怠与意义感缺失的结构性来源。</v>
+      </c>
+      <c r="G22" t="str">
+        <v>觉得身不由己、怀疑自己能力、专业孤立无人理解</v>
+      </c>
+      <c r="H22" t="str">
+        <v>工作边界模糊+成就感延迟+专业孤立</v>
+      </c>
+      <c r="I22" t="str">
+        <v>用 BPNSF 定位最缺的需要，从工作环境与个人调节两个层面同时改善</v>
+      </c>
+      <c r="J22" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SG_AT_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>家长沟通压力</v>
+      </c>
+      <c r="C23" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D23" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E23" t="str">
+        <v>self_growth,relation,parent</v>
+      </c>
+      <c r="F23" t="str">
+        <v>家长沟通频率压力、边界侵犯感与情绪影响，是小学班主任第一压力源。</v>
+      </c>
+      <c r="G23" t="str">
+        <v>非工作时间被联系、被投诉后自我怀疑、被过度监督</v>
+      </c>
+      <c r="H23" t="str">
+        <v>家长高频率联系、责任推诿、过度关注型家长多</v>
+      </c>
+      <c r="I23" t="str">
+        <v>用信息分流系统分类响应消息，配合家长预期管理话术建立家校同盟</v>
+      </c>
+      <c r="J23" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SG_AT_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>任务过载</v>
+      </c>
+      <c r="C24" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D24" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E24" t="str">
+        <v>self_growth,workload</v>
+      </c>
+      <c r="F24" t="str">
+        <v>待办堆积、非教学任务挤占时间导致焦虑性忙碌，失去掌控感。</v>
+      </c>
+      <c r="G24" t="str">
+        <v>待办清单超 10 项、感觉永远做不完、焦虑性忙碌</v>
+      </c>
+      <c r="H24" t="str">
+        <v>非教学任务挤占+不会委托+不会拒绝</v>
+      </c>
+      <c r="I24" t="str">
+        <v>用任务剃刀三把刀（删除/委托/降级）削减 50% 非必要任务</v>
+      </c>
+      <c r="J24" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SG_AT_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>时间碎片化</v>
+      </c>
+      <c r="C25" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D25" t="str">
+        <v>1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>self_growth,workload</v>
+      </c>
+      <c r="F25" t="str">
+        <v>注意力被不断打断，缺乏整块深度工作时间，感觉很忙但没产出。</v>
+      </c>
+      <c r="G25" t="str">
+        <v>随时回消息、难有整块时间、切换成本过高</v>
+      </c>
+      <c r="H25" t="str">
+        <v>信息无分流、无时间块规划、边界未建立</v>
+      </c>
+      <c r="I25" t="str">
+        <v>用信息隔离时段+时间块规划保护深度工作时间</v>
+      </c>
+      <c r="J25" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SG_AT_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>拖延回避</v>
+      </c>
+      <c r="C26" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D26" t="str">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>self_growth,workload</v>
+      </c>
+      <c r="F26" t="str">
+        <v>小任务堆积、重要事项不推进，启动困难导致恶性循环。</v>
+      </c>
+      <c r="G26" t="str">
+        <v>「等一下」就永远没做、DDL 前赶工、多任务并行无产出</v>
+      </c>
+      <c r="H26" t="str">
+        <v>任务过大无拆解+启动困难+完美主义前置</v>
+      </c>
+      <c r="I26" t="str">
+        <v>用两分钟闪电战消灭微任务，配合微成功阶梯降低启动门槛</v>
+      </c>
+      <c r="J26" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SG_AT_26</v>
+      </c>
+      <c r="B27" t="str">
         <v>支持系统缺失</v>
       </c>
-      <c r="C6" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="D6" t="str">
+      <c r="C27" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D27" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E27" t="str">
+        <v>self_growth,support</v>
+      </c>
+      <c r="F27" t="str">
+        <v>缺少可求助的同伴与制度通道，独自消化问题，43.18% 班主任无法获得有效系统支持。</v>
+      </c>
+      <c r="G27" t="str">
+        <v>独自消化问题、不主动求助、认为求助等于无能</v>
+      </c>
+      <c r="H27" t="str">
+        <v>教研组协作弱、校内缺少同伴支持机制、求助曾被拒</v>
+      </c>
+      <c r="I27" t="str">
+        <v>建立同伴支持二人组，每周一次结构化支持性对话；梳理资源地图</v>
+      </c>
+      <c r="J27" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SG_AT_27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>关系疏离</v>
+      </c>
+      <c r="C28" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D28" t="str">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>self_growth,relation</v>
+      </c>
+      <c r="F28" t="str">
+        <v>师生/同事关系停留在事务层面，情感连接缺失，师生关系功利化。</v>
+      </c>
+      <c r="G28" t="str">
+        <v>和学生只谈管理、感受不到连接的意义、同事间无真正交流</v>
+      </c>
+      <c r="H28" t="str">
+        <v>高强度事务挤压情感连接时间、用标准代替感受</v>
+      </c>
+      <c r="I28" t="str">
+        <v>用五分钟深度连接与学生做非学业对话，配合角色转换体验恢复同理心</v>
+      </c>
+      <c r="J28" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SG_AT_28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>防御退缩</v>
+      </c>
+      <c r="C29" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D29" t="str">
         <v>1.1</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E29" t="str">
         <v>self_growth,support</v>
       </c>
-      <c r="F6" t="str">
-        <v>教师遇到困难时缺少可求助的同伴或制度通道，独自消化问题。</v>
-      </c>
-      <c r="G6" t="str">
-        <v>独自消化问题、不主动求助、认为求助等于无能</v>
-      </c>
-      <c r="H6" t="str">
-        <v>教研组协作弱或校内缺少同伴支持机制</v>
-      </c>
-      <c r="I6" t="str">
-        <v>本周找一位同事做一次 20 分钟的结构化复盘，只说事实、感受和需要的支持</v>
-      </c>
-      <c r="J6" t="str">
-        <v>自我成长赋能手册v1</v>
+      <c r="F29" t="str">
+        <v>尝试后觉得没用，放弃寻找意义与连接，回避深度情感（E 防御-退缩模式）。</v>
+      </c>
+      <c r="G29" t="str">
+        <v>回避与学生深度情感连接、用物质奖励替代情感回应、放弃尝试</v>
+      </c>
+      <c r="H29" t="str">
+        <v>多次受挫+求助被拒+系统支持缺失</v>
+      </c>
+      <c r="I29" t="str">
+        <v>通过同行配对提供安全的一对一关系，不强迫干预，必要时专业支持转介</v>
+      </c>
+      <c r="J29" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SG_AT_29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>自我关怀不足</v>
+      </c>
+      <c r="C30" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D30" t="str">
+        <v>1</v>
+      </c>
+      <c r="E30" t="str">
+        <v>self_growth,selfcare</v>
+      </c>
+      <c r="F30" t="str">
+        <v>忙于照顾所有人却忘了照顾自己，对自己苛刻，基本自我照顾被牺牲。</v>
+      </c>
+      <c r="G30" t="str">
+        <v>一天没吃没喝没休息、自我攻击「我不配」</v>
+      </c>
+      <c r="H30" t="str">
+        <v>责任感过强+自我批评习惯+「先人后己」信念</v>
+      </c>
+      <c r="I30" t="str">
+        <v>用自我关怀休息三步（正念→共通人性→自我善意），每天对照自我照顾清单打勾</v>
+      </c>
+      <c r="J30" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SG_AT_30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>工作生活失衡</v>
+      </c>
+      <c r="C31" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D31" t="str">
+        <v>1</v>
+      </c>
+      <c r="E31" t="str">
+        <v>self_growth,boundary</v>
+      </c>
+      <c r="F31" t="str">
+        <v>工作与个人生活边界消失，下班后大脑仍持续运转，无法切换模式。</v>
+      </c>
+      <c r="G31" t="str">
+        <v>下班脑中仍想工作、周末还在想工作、对周一抗拒</v>
+      </c>
+      <c r="H31" t="str">
+        <v>无结束仪式、手机成为「隐形办公室」、不回消息焦虑</v>
+      </c>
+      <c r="I31" t="str">
+        <v>用每日三件删除+周末清零仪式建立工作结束信号</v>
+      </c>
+      <c r="J31" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SG_AT_31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>AI焦虑</v>
+      </c>
+      <c r="C32" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="D32" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="E32" t="str">
+        <v>self_growth,cognition,ai</v>
+      </c>
+      <c r="F32" t="str">
+        <v>AI 技术发展带来的职业价值不确定感，是影响教师幸福感的第二大因素。</v>
+      </c>
+      <c r="G32" t="str">
+        <v>担心被 AI 取代、跟不上技术发展、对职业价值感到焦虑</v>
+      </c>
+      <c r="H32" t="str">
+        <v>数字素养差异大、对职业价值的 existential 焦虑</v>
+      </c>
+      <c r="I32" t="str">
+        <v>用「我的不可替代性」反思列出 AI 做不到的事，配合本周小尝试微步式提升数字自信</v>
+      </c>
+      <c r="J32" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J32"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -703,10 +1535,10 @@
         <v>2.5</v>
       </c>
       <c r="F2" t="str">
-        <v>疲惫题项处于高位，情绪资源已被大量消耗</v>
+        <v>疲惫题项处于高位，情绪资源大量消耗</v>
       </c>
       <c r="G2" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -714,22 +1546,22 @@
         <v>SG_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="D3" t="str">
-        <v>题[q1] &gt;= 3</v>
+        <v>维度[SG_S3D2] &gt;= 4</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="str">
-        <v>疲惫题项高于常模均值，处于早期消耗阶段</v>
+        <v>「下班后精力完全耗尽」高频出现</v>
       </c>
       <c r="G3" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -737,22 +1569,22 @@
         <v>SG_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_AT_02</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="C4" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="D4" t="str">
-        <v>题[q2] &gt;= 4</v>
+        <v>维度[SG_S3D10] &gt;= 2</v>
       </c>
       <c r="E4" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>频繁出现「什么都是我的责任」的感受</v>
+        <v>入睡时间超过 30 分钟，睡眠问题明显</v>
       </c>
       <c r="G4" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -760,22 +1592,22 @@
         <v>SG_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_AT_02</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="D5" t="str">
-        <v>题[q2] &gt;= 3</v>
+        <v>维度[SG_S3D9] &gt;= 4</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="str">
-        <v>责任边界开始模糊</v>
+        <v>「已经到了承受的极限」高频出现</v>
       </c>
       <c r="G5" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -783,22 +1615,22 @@
         <v>SG_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_S1</v>
+        <v>SG_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>题[q3] &gt;= 4</v>
+        <v>维度[SG_S2D4] &lt;= 8</v>
       </c>
       <c r="E6" t="str">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="str">
-        <v>意义感知处于低位（反向计分后得分高）</v>
+        <v>职业乐观维度偏低，倾向预期负面结果</v>
       </c>
       <c r="G6" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="7">
@@ -806,22 +1638,22 @@
         <v>SG_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_06</v>
       </c>
       <c r="C7" t="str">
-        <v>SG_S1</v>
+        <v>SG_S2</v>
       </c>
       <c r="D7" t="str">
-        <v>题[q3] &gt;= 3</v>
+        <v>维度[SG_S2D7] &lt;= 3</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="str">
-        <v>意义感出现波动</v>
+        <v>情感挫折后难以找到恢复安全感的方式</v>
       </c>
       <c r="G7" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="8">
@@ -829,22 +1661,22 @@
         <v>SG_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_07</v>
       </c>
       <c r="C8" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="D8" t="str">
-        <v>题[q4] &gt;= 4</v>
+        <v>维度[SG_S3D8] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F8" t="str">
-        <v>面对复杂问题时效能信心不足</v>
+        <v>直接与人打交道带来的压力处于高位</v>
       </c>
       <c r="G8" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="9">
@@ -852,22 +1684,22 @@
         <v>SG_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_08</v>
       </c>
       <c r="C9" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="D9" t="str">
-        <v>题[q4] &gt;= 3</v>
+        <v>维度[SG_S3D4] &gt;= 4</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="str">
-        <v>效能信心有所下降</v>
+        <v>整天与人打交道带来的压力处于高位</v>
       </c>
       <c r="G9" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="10">
@@ -875,22 +1707,22 @@
         <v>SG_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_AT_05</v>
+        <v>SG_AT_09</v>
       </c>
       <c r="C10" t="str">
-        <v>SG_S1</v>
+        <v>SG_S2</v>
       </c>
       <c r="D10" t="str">
-        <v>题[q5] &gt;= 4</v>
+        <v>维度[SG_S2D5] &lt;= 3</v>
       </c>
       <c r="E10" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F10" t="str">
-        <v>工作困难长期无人分担</v>
+        <v>面对学生强烈情感需求难以稳定回应</v>
       </c>
       <c r="G10" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="11">
@@ -898,22 +1730,22 @@
         <v>SG_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SG_AT_05</v>
+        <v>SG_AT_10</v>
       </c>
       <c r="C11" t="str">
         <v>SG_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>题[q5] &gt;= 3</v>
+        <v>题[q2] &gt;= 4</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F11" t="str">
-        <v>支持来源不够稳定</v>
+        <v>频繁出现「什么都是我的责任」</v>
       </c>
       <c r="G11" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="12">
@@ -921,22 +1753,22 @@
         <v>SG_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_11</v>
       </c>
       <c r="C12" t="str">
-        <v>SG_S1</v>
+        <v>SG_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>维度[SG_S2D8] &gt;= 4</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F12" t="str">
-        <v>疲惫与意义感同时告急，是情绪耗竭的核心信号</v>
+        <v>非工作时间被联系、边界被侵犯感受强烈</v>
       </c>
       <c r="G12" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="13">
@@ -944,22 +1776,22 @@
         <v>SG_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_12</v>
       </c>
       <c r="C13" t="str">
-        <v>SG_S2</v>
+        <v>SG_S3</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SG_S2D2] &gt;= 3.5</v>
+        <v>维度[SG_S3D7] &gt;= 4</v>
       </c>
       <c r="E13" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F13" t="str">
-        <v>HERO 效能维度偏低</v>
+        <v>「工作太拼命」频率高，完美主义倾向</v>
       </c>
       <c r="G13" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="14">
@@ -967,22 +1799,22 @@
         <v>SG_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_13</v>
       </c>
       <c r="C14" t="str">
-        <v>SG_S2</v>
+        <v>SG_S3</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SG_S2D3] &gt;= 3.5</v>
+        <v>维度[SG_S3D29] &gt;= 4</v>
       </c>
       <c r="E14" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F14" t="str">
-        <v>HERO 韧性维度偏低，受挫后恢复困难</v>
+        <v>面对质疑投诉时自我怀疑明显</v>
       </c>
       <c r="G14" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="15">
@@ -990,22 +1822,22 @@
         <v>SG_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_14</v>
       </c>
       <c r="C15" t="str">
-        <v>SG_S2</v>
+        <v>SG_S3</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SG_S2D1] &gt;= 3.5</v>
+        <v>维度[SG_S3D29] &gt;= 3</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>HERO 希望维度偏低，看不到可行路径</v>
+        <v>自我怀疑出现，存在冒名顶替倾向</v>
       </c>
       <c r="G15" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="16">
@@ -1013,34 +1845,402 @@
         <v>SG_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_15</v>
       </c>
       <c r="C16" t="str">
         <v>SG_S2</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SG_S2D4] &gt;= 3.5</v>
+        <v>维度[SG_S2D2] &lt;= 8 且 维度[SG_S2D1] &lt;= 8</v>
       </c>
       <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>职业效能与职业希望双低，认知锁定风险</v>
+      </c>
+      <c r="G16" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_EV_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SG_AT_16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="D17" t="str">
+        <v>题[q3] &gt;= 4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>3</v>
+      </c>
+      <c r="F17" t="str">
+        <v>意义感知处于低位（反向计分后得分高）</v>
+      </c>
+      <c r="G17" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_EV_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SG_AT_17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D18" t="str">
+        <v>维度[SG_S3D22] &lt;= 3</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>职业价值认同偏低（1-5 分制）</v>
+      </c>
+      <c r="G18" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_EV_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>SG_AT_18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="D19" t="str">
+        <v>总分 &lt;= 31</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>HERO 总分 24-31 分中度风险区间</v>
+      </c>
+      <c r="G19" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_EV_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SG_AT_19</v>
+      </c>
+      <c r="C20" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="D20" t="str">
+        <v>题[q4] &gt;= 4</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2</v>
+      </c>
+      <c r="F20" t="str">
+        <v>处理棘手问题的信心不足（反向计分后得分高）</v>
+      </c>
+      <c r="G20" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SG_EV_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SG_AT_20</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="D21" t="str">
+        <v>维度[SG_S2D3] &lt;= 8</v>
+      </c>
+      <c r="E21" t="str">
         <v>1.5</v>
       </c>
-      <c r="F16" t="str">
-        <v>HERO 乐观维度偏低</v>
-      </c>
-      <c r="G16" t="str">
-        <v>自我成长赋能手册v1</v>
+      <c r="F21" t="str">
+        <v>职业韧性维度偏低，受挫后恢复困难</v>
+      </c>
+      <c r="G21" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SG_EV_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SG_AT_21</v>
+      </c>
+      <c r="C22" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D22" t="str">
+        <v>维度[SG_S3D19] &lt;= 9</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F22" t="str">
+        <v>自主需要满足度低（3 题和 3-21 分）</v>
+      </c>
+      <c r="G22" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SG_EV_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SG_AT_22</v>
+      </c>
+      <c r="C23" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D23" t="str">
+        <v>维度[SG_S3D32] &gt;= 4</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>家长指责教师管理不到位的情况明显</v>
+      </c>
+      <c r="G23" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SG_EV_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SG_AT_23</v>
+      </c>
+      <c r="C24" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="D24" t="str">
+        <v>维度[SG_S2D10] &gt;= 4</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F24" t="str">
+        <v>家长沟通挤占备课与休息时间明显</v>
+      </c>
+      <c r="G24" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SG_EV_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SG_AT_24</v>
+      </c>
+      <c r="C25" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D25" t="str">
+        <v>维度[SG_S3D30] &gt;= 3</v>
+      </c>
+      <c r="E25" t="str">
+        <v>1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>时间被消息与事务大量挤占</v>
+      </c>
+      <c r="G25" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SG_EV_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SG_AT_25</v>
+      </c>
+      <c r="C26" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="D26" t="str">
+        <v>维度[SG_S2D1] &lt;= 9</v>
+      </c>
+      <c r="E26" t="str">
+        <v>1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>职业希望偏低，缺少规划与启动动力</v>
+      </c>
+      <c r="G26" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SG_EV_26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SG_AT_26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="D27" t="str">
+        <v>题[q5] &gt;= 4</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F27" t="str">
+        <v>工作困难长期无人分担</v>
+      </c>
+      <c r="G27" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SG_EV_27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SG_AT_27</v>
+      </c>
+      <c r="C28" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D28" t="str">
+        <v>维度[SG_S3D21] &lt;= 9</v>
+      </c>
+      <c r="E28" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F28" t="str">
+        <v>关系需要满足度低，情感连接缺失</v>
+      </c>
+      <c r="G28" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SG_EV_28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>SG_AT_28</v>
+      </c>
+      <c r="C29" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D29" t="str">
+        <v>维度[SG_S3D21] &lt;= 6</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2</v>
+      </c>
+      <c r="F29" t="str">
+        <v>关系需要严重受挫，倾向防御退缩</v>
+      </c>
+      <c r="G29" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SG_EV_29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>SG_AT_29</v>
+      </c>
+      <c r="C30" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="D30" t="str">
+        <v>维度[SG_S3D13] &gt;= 2</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F30" t="str">
+        <v>睡眠效率偏低，基本自我照顾被牺牲</v>
+      </c>
+      <c r="G30" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SG_EV_30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>SG_AT_30</v>
+      </c>
+      <c r="C31" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="D31" t="str">
+        <v>维度[SG_S2D8] &gt;= 3</v>
+      </c>
+      <c r="E31" t="str">
+        <v>1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>非工作时间被占用，工作生活边界模糊</v>
+      </c>
+      <c r="G31" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SG_EV_31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SG_AT_31</v>
+      </c>
+      <c r="C32" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="D32" t="str">
+        <v>维度[SG_S2D4] &lt;= 6</v>
+      </c>
+      <c r="E32" t="str">
+        <v>1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>职业乐观严重偏低，存在职业价值焦虑</v>
+      </c>
+      <c r="G32" t="str">
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G32"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1106,7 +2306,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 5 且 题[q3] &gt;= 4</v>
+        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
         <v>red</v>
@@ -1139,7 +2339,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -1150,19 +2350,19 @@
         <v>self_growth</v>
       </c>
       <c r="C3" t="str">
-        <v>SG_S2</v>
+        <v>SG_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 20</v>
       </c>
       <c r="F3" t="str">
         <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>需关注</v>
+        <v>重度风险</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1171,16 +2371,16 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
+        <v>五问自评总分≥20，启动支持响应。</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次深评仍为红色</v>
+        <v>连续两次评估仍为重度风险</v>
       </c>
       <c r="L3" t="str">
         <v>年级组长</v>
       </c>
       <c r="M3" t="str">
-        <v>14天后复评</v>
+        <v>14 天后复评</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -1189,7 +2389,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -1206,13 +2406,13 @@
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>总分 &lt;= 31</v>
       </c>
       <c r="F4" t="str">
         <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>关注</v>
+        <v>明显消耗</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1221,7 +2421,7 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>心理资本出现波动，建议做针对性调整。</v>
+        <v>HERO 心理资本处于中度消耗区间，建议针对性调整。</v>
       </c>
       <c r="K4" t="str">
         <v>连续两次深评均分未下降</v>
@@ -1230,7 +2430,7 @@
         <v>年级组长</v>
       </c>
       <c r="M4" t="str">
-        <v>30天后复评</v>
+        <v>30 天后复评</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -1239,48 +2439,48 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_GR_AUTO_01</v>
+        <v>SG_GR_04</v>
       </c>
       <c r="B5" t="str">
         <v>self_growth</v>
       </c>
       <c r="C5" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>维度[SG_S3D1] &gt;= 3</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>需关注</v>
+        <v>轻度关注</v>
       </c>
       <c r="H5" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
+        <v>六维深度评估中情绪耗竭维度开始出现信号。</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>复评时信号加重</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>30 天后复评</v>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -1289,39 +2489,39 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_GR_AUTO_02</v>
+        <v>SG_GR_DEFAULT</v>
       </c>
       <c r="B6" t="str">
         <v>self_growth</v>
       </c>
       <c r="C6" t="str">
-        <v>SG_S1</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>999</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>green</v>
       </c>
       <c r="G6" t="str">
-        <v>关注</v>
+        <v>状态良好</v>
       </c>
       <c r="H6" t="str">
-        <v>medium</v>
+        <v>low</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>心理资本出现波动，建议做针对性调整。</v>
+        <v>本次评估未发现需要重点干预的信号</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -1339,162 +2539,12 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>SG_GR_AUTO_03</v>
-      </c>
-      <c r="B7" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C7" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="D7" t="str">
-        <v>503</v>
-      </c>
-      <c r="E7" t="str">
-        <v>均分 &gt;= 4</v>
-      </c>
-      <c r="F7" t="str">
-        <v>orange</v>
-      </c>
-      <c r="G7" t="str">
-        <v>需关注</v>
-      </c>
-      <c r="H7" t="str">
-        <v>high</v>
-      </c>
-      <c r="I7" t="str">
-        <v>否</v>
-      </c>
-      <c r="J7" t="str">
-        <v>心理资本多个维度处于低位，建议本周内安排一次支持性沟通。</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>SG_GR_AUTO_04</v>
-      </c>
-      <c r="B8" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C8" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="D8" t="str">
-        <v>504</v>
-      </c>
-      <c r="E8" t="str">
-        <v>均分 &gt;= 3.5</v>
-      </c>
-      <c r="F8" t="str">
-        <v>yellow</v>
-      </c>
-      <c r="G8" t="str">
-        <v>关注</v>
-      </c>
-      <c r="H8" t="str">
-        <v>medium</v>
-      </c>
-      <c r="I8" t="str">
-        <v>否</v>
-      </c>
-      <c r="J8" t="str">
-        <v>心理资本出现波动，建议做针对性调整。</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>SG_GR_DEFAULT</v>
-      </c>
-      <c r="B9" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>999</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>green</v>
-      </c>
-      <c r="G9" t="str">
-        <v>状态良好</v>
-      </c>
-      <c r="H9" t="str">
-        <v>low</v>
-      </c>
-      <c r="I9" t="str">
-        <v>否</v>
-      </c>
-      <c r="J9" t="str">
-        <v>本次评估未发现需要重点干预的信号</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1540,7 +2590,7 @@
         <v>self_growth</v>
       </c>
       <c r="B2" t="str">
-        <v>量表[SG_S1].题[q1] &gt;= 5 且 量表[SG_S1].题[q3] &gt;= 4</v>
+        <v>量表[SG_S1].题[q1] &gt;= 4 且 量表[SG_S1].题[q3] &gt;= 4</v>
       </c>
       <c r="C2" t="str">
         <v>疲惫与意义感同时处于高位，已暂停常规建议并生成转介工单。</v>
@@ -1549,7 +2599,7 @@
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
+        <v>立即阻断常规建议输出，展示危机求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
         <v>停止当前评估流程；展示危机求助指引；创建安全事件；生成转介工单；短信通知心理专员</v>
@@ -1564,7 +2614,7 @@
         <v>[教师姓名]老师在自我成长评估中触发红线：疲惫与意义感同时告急。请尽快登录系统查看工单。</v>
       </c>
       <c r="J2" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
